--- a/data/Products.xlsx
+++ b/data/Products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Phohouse\Documents\UiPath\MicrocenterMonitorBot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C725929-9584-471A-AF8A-D1A5978E9A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8F252E4-3DE2-4294-88B0-766B5553BFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="4695" windowWidth="38400" windowHeight="14700" xr2:uid="{8E77DD56-D862-4602-B1FB-B1FB56125B70}"/>
+    <workbookView xWindow="7005" yWindow="4695" windowWidth="38400" windowHeight="14700" xr2:uid="{9993CB73-5B39-441F-B593-BFE3AE60F3D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,22 +33,22 @@
     <t>SearchTerm</t>
   </si>
   <si>
+    <t>Ryzen 7800X3D</t>
+  </si>
+  <si>
+    <t>7800x3d</t>
+  </si>
+  <si>
+    <t>RTX 5080</t>
+  </si>
+  <si>
+    <t>rtx 5080</t>
+  </si>
+  <si>
     <t>DDR5 32GB Kit</t>
   </si>
   <si>
-    <t>32GB (2 x 16GB</t>
-  </si>
-  <si>
-    <t>Ryzen 7800X3D</t>
-  </si>
-  <si>
-    <t>7800x3d</t>
-  </si>
-  <si>
-    <t>RTX 5080</t>
-  </si>
-  <si>
-    <t>rtx 5080</t>
+    <t>32gb ddr5 ram</t>
   </si>
   <si>
     <t>2TB NVMe SSD</t>
@@ -405,13 +405,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590A8E6F-8C61-489B-95BF-531ADAF4BA29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB600A9C-31DE-423A-9487-D849C3E1F599}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -423,26 +419,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
